--- a/artfynd/Lögdaselet artfynd.xlsx
+++ b/artfynd/Lögdaselet artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126814940</v>
+        <v>126814975</v>
       </c>
       <c r="B2" t="n">
-        <v>79598</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>677606</v>
+        <v>677531</v>
       </c>
       <c r="R2" t="n">
-        <v>7109678</v>
+        <v>7109708</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126814937</v>
+        <v>126814976</v>
       </c>
       <c r="B3" t="n">
-        <v>79598</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>677539</v>
+        <v>677541</v>
       </c>
       <c r="R3" t="n">
-        <v>7109754</v>
+        <v>7109785</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126814970</v>
+        <v>126814977</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>677462</v>
+        <v>677639</v>
       </c>
       <c r="R4" t="n">
-        <v>7109378</v>
+        <v>7109768</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126814961</v>
+        <v>126814978</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677470</v>
+        <v>677588</v>
       </c>
       <c r="R5" t="n">
-        <v>7109382</v>
+        <v>7109668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814936</v>
+        <v>126814962</v>
       </c>
       <c r="B6" t="n">
-        <v>79598</v>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677536</v>
+        <v>677473</v>
       </c>
       <c r="R6" t="n">
-        <v>7109700</v>
+        <v>7109404</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,14 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126814966</v>
+        <v>126814961</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>677648</v>
+        <v>677470</v>
       </c>
       <c r="R7" t="n">
-        <v>7109697</v>
+        <v>7109382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126814956</v>
+        <v>126814963</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677528</v>
+        <v>677414</v>
       </c>
       <c r="R8" t="n">
-        <v>7109526</v>
+        <v>7109372</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126814959</v>
+        <v>126814964</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,48 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677593</v>
+        <v>677401</v>
       </c>
       <c r="R9" t="n">
-        <v>7110064</v>
+        <v>7109391</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1439,11 +1425,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>11 blomstänglar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1470,48 +1451,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1992011</v>
+        <v>126814965</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>13,7 km O om Fredrika, Ås lm</t>
+          <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>679431</v>
+        <v>677536</v>
       </c>
       <c r="R10" t="n">
-        <v>7109102</v>
+        <v>7109606</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1535,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2005-08-13</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2005-08-13</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1555,44 +1536,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126814941</v>
+        <v>126814967</v>
       </c>
       <c r="B11" t="n">
-        <v>79598</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>677590</v>
+        <v>677499</v>
       </c>
       <c r="R11" t="n">
-        <v>7109668</v>
+        <v>7109474</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1664,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126814939</v>
+        <v>126814968</v>
       </c>
       <c r="B12" t="n">
-        <v>79598</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>677539</v>
+        <v>677477</v>
       </c>
       <c r="R12" t="n">
-        <v>7109781</v>
+        <v>7109411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1761,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126814978</v>
+        <v>126814969</v>
       </c>
       <c r="B13" t="n">
-        <v>78647</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>677588</v>
+        <v>677470</v>
       </c>
       <c r="R13" t="n">
-        <v>7109668</v>
+        <v>7109386</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126814953</v>
+        <v>126814970</v>
       </c>
       <c r="B14" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677539</v>
+        <v>677462</v>
       </c>
       <c r="R14" t="n">
-        <v>7109754</v>
+        <v>7109378</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,54 +1936,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126814960</v>
+        <v>126814979</v>
       </c>
       <c r="B15" t="n">
-        <v>98361</v>
+        <v>78730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>677579</v>
+        <v>677601</v>
       </c>
       <c r="R15" t="n">
-        <v>7110002</v>
+        <v>7109964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126814934</v>
+        <v>126814980</v>
       </c>
       <c r="B16" t="n">
-        <v>79598</v>
+        <v>78730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2072,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2096,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>677547</v>
+        <v>677538</v>
       </c>
       <c r="R16" t="n">
-        <v>7109670</v>
+        <v>7109554</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126814948</v>
+        <v>126814943</v>
       </c>
       <c r="B17" t="n">
-        <v>80112</v>
+        <v>83307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2193,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>677527</v>
+        <v>677425</v>
       </c>
       <c r="R17" t="n">
-        <v>7109586</v>
+        <v>7109375</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126814946</v>
+        <v>126814944</v>
       </c>
       <c r="B18" t="n">
-        <v>79569</v>
+        <v>83307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2266,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2290,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>677600</v>
+        <v>677465</v>
       </c>
       <c r="R18" t="n">
-        <v>7109963</v>
+        <v>7109391</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,7 +2327,7 @@
         <v>126814945</v>
       </c>
       <c r="B19" t="n">
-        <v>75075</v>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126814969</v>
+        <v>126814934</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2460,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2484,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>677470</v>
+        <v>677547</v>
       </c>
       <c r="R20" t="n">
-        <v>7109386</v>
+        <v>7109670</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2546,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126814952</v>
+        <v>126814936</v>
       </c>
       <c r="B21" t="n">
-        <v>80111</v>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2581,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>677621</v>
+        <v>677536</v>
       </c>
       <c r="R21" t="n">
-        <v>7109689</v>
+        <v>7109700</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2643,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126814967</v>
+        <v>126814937</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2654,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2678,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>677499</v>
+        <v>677539</v>
       </c>
       <c r="R22" t="n">
-        <v>7109474</v>
+        <v>7109754</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2740,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126814963</v>
+        <v>126814938</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2751,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2775,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>677414</v>
+        <v>677543</v>
       </c>
       <c r="R23" t="n">
-        <v>7109372</v>
+        <v>7109764</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2837,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126814943</v>
+        <v>126814939</v>
       </c>
       <c r="B24" t="n">
-        <v>75075</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2848,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2872,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>677425</v>
+        <v>677539</v>
       </c>
       <c r="R24" t="n">
-        <v>7109375</v>
+        <v>7109781</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2934,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126814947</v>
+        <v>126814940</v>
       </c>
       <c r="B25" t="n">
-        <v>79569</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2945,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2969,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>677535</v>
+        <v>677606</v>
       </c>
       <c r="R25" t="n">
-        <v>7109555</v>
+        <v>7109678</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3031,45 +3003,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126837623</v>
+        <v>126814941</v>
       </c>
       <c r="B26" t="n">
-        <v>98382</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storaggan S om, Ås lm</t>
+          <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>677483</v>
+        <v>677590</v>
       </c>
       <c r="R26" t="n">
-        <v>7109385</v>
+        <v>7109668</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3116,26 +3088,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1991798</v>
+        <v>126814955</v>
       </c>
       <c r="B27" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3163,17 +3131,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>13,2 km O om Fredrika, Ås lm</t>
+          <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>678980</v>
+        <v>677526</v>
       </c>
       <c r="R27" t="n">
-        <v>7109235</v>
+        <v>7109531</v>
       </c>
       <c r="S27" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3197,12 +3165,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2005-08-09</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2005-08-09</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3217,44 +3185,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126814949</v>
+        <v>126814956</v>
       </c>
       <c r="B28" t="n">
-        <v>80112</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3264,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>677526</v>
+        <v>677528</v>
       </c>
       <c r="R28" t="n">
-        <v>7109531</v>
+        <v>7109526</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3326,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126814938</v>
+        <v>126814952</v>
       </c>
       <c r="B29" t="n">
-        <v>79598</v>
+        <v>80460</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3361,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>677543</v>
+        <v>677621</v>
       </c>
       <c r="R29" t="n">
-        <v>7109764</v>
+        <v>7109689</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3423,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126814976</v>
+        <v>126814948</v>
       </c>
       <c r="B30" t="n">
-        <v>78647</v>
+        <v>80461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3458,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>677541</v>
+        <v>677527</v>
       </c>
       <c r="R30" t="n">
-        <v>7109785</v>
+        <v>7109586</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3520,10 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126837620</v>
+        <v>126814949</v>
       </c>
       <c r="B31" t="n">
-        <v>80112</v>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3551,14 +3519,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storaggan S om, Ås lm</t>
+          <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>677537</v>
+        <v>677526</v>
       </c>
       <c r="R31" t="n">
-        <v>7109567</v>
+        <v>7109531</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3605,48 +3573,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126814957</v>
+        <v>126814950</v>
       </c>
       <c r="B32" t="n">
-        <v>77934</v>
+        <v>80461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3656,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>677462</v>
+        <v>677528</v>
       </c>
       <c r="R32" t="n">
-        <v>7109379</v>
+        <v>7109526</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3718,45 +3682,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126814964</v>
+        <v>126837620</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>80461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Storaggan, Ås lm</t>
+          <t>Storaggan S om, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>677401</v>
+        <v>677537</v>
       </c>
       <c r="R33" t="n">
-        <v>7109391</v>
+        <v>7109567</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3803,44 +3767,48 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126814979</v>
+        <v>126814954</v>
       </c>
       <c r="B34" t="n">
-        <v>78386</v>
+        <v>80468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6437</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3850,10 +3818,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>677601</v>
+        <v>677469</v>
       </c>
       <c r="R34" t="n">
-        <v>7109964</v>
+        <v>7109383</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3886,6 +3854,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På grov gammal rönn</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3912,32 +3885,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126814944</v>
+        <v>126814951</v>
       </c>
       <c r="B35" t="n">
-        <v>75075</v>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3947,10 +3920,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>677465</v>
+        <v>677608</v>
       </c>
       <c r="R35" t="n">
-        <v>7109391</v>
+        <v>7109815</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4009,47 +3982,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126814958</v>
+        <v>126814974</v>
       </c>
       <c r="B36" t="n">
-        <v>98361</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4058,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>677595</v>
+        <v>677466</v>
       </c>
       <c r="R36" t="n">
-        <v>7110068</v>
+        <v>7109379</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4120,32 +4084,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126814975</v>
+        <v>126814972</v>
       </c>
       <c r="B37" t="n">
-        <v>78647</v>
+        <v>99035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>219790</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4155,10 +4119,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>677531</v>
+        <v>677402</v>
       </c>
       <c r="R37" t="n">
-        <v>7109708</v>
+        <v>7109377</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4217,32 +4181,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126814951</v>
+        <v>126814973</v>
       </c>
       <c r="B38" t="n">
-        <v>57654</v>
+        <v>99035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4252,10 +4216,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>677608</v>
+        <v>677529</v>
       </c>
       <c r="R38" t="n">
-        <v>7109815</v>
+        <v>7109595</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4314,45 +4278,59 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126814968</v>
+        <v>126814958</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>677477</v>
+        <v>677595</v>
       </c>
       <c r="R39" t="n">
-        <v>7109411</v>
+        <v>7110068</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4411,45 +4389,59 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126814954</v>
+        <v>126814959</v>
       </c>
       <c r="B40" t="n">
-        <v>80119</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>677469</v>
+        <v>677593</v>
       </c>
       <c r="R40" t="n">
-        <v>7109383</v>
+        <v>7110064</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4486,7 +4478,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På grov gammal rönn</t>
+          <t>11 blomstänglar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4513,45 +4505,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126814980</v>
+        <v>126814960</v>
       </c>
       <c r="B41" t="n">
-        <v>78386</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>677538</v>
+        <v>677579</v>
       </c>
       <c r="R41" t="n">
-        <v>7109554</v>
+        <v>7110002</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4610,45 +4611,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126814962</v>
+        <v>126837623</v>
       </c>
       <c r="B42" t="n">
-        <v>82792</v>
+        <v>99140</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storaggan, Ås lm</t>
+          <t>Storaggan S om, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>677473</v>
+        <v>677483</v>
       </c>
       <c r="R42" t="n">
-        <v>7109404</v>
+        <v>7109385</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4695,22 +4696,26 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126814974</v>
+        <v>126814957</v>
       </c>
       <c r="B43" t="n">
-        <v>57657</v>
+        <v>78339</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4718,36 +4723,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>677466</v>
+        <v>677462</v>
       </c>
       <c r="R43" t="n">
         <v>7109379</v>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126814965</v>
+        <v>126814953</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>79085</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>677536</v>
+        <v>677539</v>
       </c>
       <c r="R44" t="n">
-        <v>7109606</v>
+        <v>7109754</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4906,32 +4906,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126814972</v>
+        <v>126814946</v>
       </c>
       <c r="B45" t="n">
-        <v>98278</v>
+        <v>79917</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>677402</v>
+        <v>677600</v>
       </c>
       <c r="R45" t="n">
-        <v>7109377</v>
+        <v>7109963</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5003,32 +5003,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126814973</v>
+        <v>126814947</v>
       </c>
       <c r="B46" t="n">
-        <v>98278</v>
+        <v>79917</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>677529</v>
+        <v>677535</v>
       </c>
       <c r="R46" t="n">
-        <v>7109595</v>
+        <v>7109555</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5100,32 +5100,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126814977</v>
+        <v>126814966</v>
       </c>
       <c r="B47" t="n">
-        <v>78647</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>677639</v>
+        <v>677648</v>
       </c>
       <c r="R47" t="n">
-        <v>7109768</v>
+        <v>7109697</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5197,48 +5197,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126814950</v>
+        <v>1991798</v>
       </c>
       <c r="B48" t="n">
-        <v>80112</v>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Storaggan, Ås lm</t>
+          <t>13,2 km O om Fredrika, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>677528</v>
+        <v>678980</v>
       </c>
       <c r="R48" t="n">
-        <v>7109526</v>
+        <v>7109235</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5262,12 +5262,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2005-08-09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2005-08-09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5282,22 +5282,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126814955</v>
+        <v>1992011</v>
       </c>
       <c r="B49" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5325,17 +5325,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storaggan, Ås lm</t>
+          <t>13,7 km O om Fredrika, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>677526</v>
+        <v>679431</v>
       </c>
       <c r="R49" t="n">
-        <v>7109531</v>
+        <v>7109102</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5359,12 +5359,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2005-08-13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2005-08-13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5379,12 +5379,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
